--- a/Material/2. Interviews & Surveys/3. Quantitative Survey/table_for_predictive.xlsx
+++ b/Material/2. Interviews & Surveys/3. Quantitative Survey/table_for_predictive.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM123"/>
+  <dimension ref="A1:AM126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -736,7 +736,7 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -1093,7 +1093,7 @@
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -1212,7 +1212,7 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1331,7 +1331,7 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -1569,7 +1569,7 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1688,7 +1688,7 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -2045,7 +2045,7 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -2164,7 +2164,7 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -2640,7 +2640,7 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -2759,7 +2759,7 @@
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -2878,7 +2878,7 @@
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -3116,7 +3116,7 @@
         <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -3235,7 +3235,7 @@
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -3354,7 +3354,7 @@
         <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -3473,7 +3473,7 @@
         <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -3592,7 +3592,7 @@
         <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -3711,7 +3711,7 @@
         <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -3949,7 +3949,7 @@
         <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -4544,7 +4544,7 @@
         <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -4663,7 +4663,7 @@
         <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -4782,7 +4782,7 @@
         <v>1</v>
       </c>
       <c r="AM36" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -5139,7 +5139,7 @@
         <v>0</v>
       </c>
       <c r="AM39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -5258,7 +5258,7 @@
         <v>0</v>
       </c>
       <c r="AM40" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -5377,7 +5377,7 @@
         <v>0</v>
       </c>
       <c r="AM41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -5853,7 +5853,7 @@
         <v>0</v>
       </c>
       <c r="AM45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -6091,7 +6091,7 @@
         <v>0</v>
       </c>
       <c r="AM47" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -6329,7 +6329,7 @@
         <v>0</v>
       </c>
       <c r="AM49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -6448,7 +6448,7 @@
         <v>0</v>
       </c>
       <c r="AM50" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -6686,7 +6686,7 @@
         <v>0</v>
       </c>
       <c r="AM52" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -7162,7 +7162,7 @@
         <v>0</v>
       </c>
       <c r="AM56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -7400,7 +7400,7 @@
         <v>0</v>
       </c>
       <c r="AM58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -7876,7 +7876,7 @@
         <v>0</v>
       </c>
       <c r="AM62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -7995,7 +7995,7 @@
         <v>0</v>
       </c>
       <c r="AM63" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -8471,7 +8471,7 @@
         <v>0</v>
       </c>
       <c r="AM67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -8709,7 +8709,7 @@
         <v>0</v>
       </c>
       <c r="AM69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -8828,7 +8828,7 @@
         <v>0</v>
       </c>
       <c r="AM70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -9185,7 +9185,7 @@
         <v>0</v>
       </c>
       <c r="AM73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -9304,7 +9304,7 @@
         <v>0</v>
       </c>
       <c r="AM74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -9423,7 +9423,7 @@
         <v>0</v>
       </c>
       <c r="AM75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
@@ -9542,7 +9542,7 @@
         <v>0</v>
       </c>
       <c r="AM76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -10018,7 +10018,7 @@
         <v>0</v>
       </c>
       <c r="AM80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -10137,7 +10137,7 @@
         <v>0</v>
       </c>
       <c r="AM81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -10375,7 +10375,7 @@
         <v>0</v>
       </c>
       <c r="AM83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -10494,7 +10494,7 @@
         <v>0</v>
       </c>
       <c r="AM84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -10732,7 +10732,7 @@
         <v>0</v>
       </c>
       <c r="AM86" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
@@ -10851,7 +10851,7 @@
         <v>0</v>
       </c>
       <c r="AM87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
@@ -10970,7 +10970,7 @@
         <v>0</v>
       </c>
       <c r="AM88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
@@ -11327,7 +11327,7 @@
         <v>0</v>
       </c>
       <c r="AM91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -11446,7 +11446,7 @@
         <v>0</v>
       </c>
       <c r="AM92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
@@ -11684,7 +11684,7 @@
         <v>0</v>
       </c>
       <c r="AM94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -11803,7 +11803,7 @@
         <v>0</v>
       </c>
       <c r="AM95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -12279,7 +12279,7 @@
         <v>0</v>
       </c>
       <c r="AM99" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100">
@@ -12755,7 +12755,7 @@
         <v>0</v>
       </c>
       <c r="AM103" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -12874,7 +12874,7 @@
         <v>0</v>
       </c>
       <c r="AM104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -12993,7 +12993,7 @@
         <v>0</v>
       </c>
       <c r="AM105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -13112,7 +13112,7 @@
         <v>0</v>
       </c>
       <c r="AM106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -13350,7 +13350,7 @@
         <v>0</v>
       </c>
       <c r="AM108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -13588,7 +13588,7 @@
         <v>0</v>
       </c>
       <c r="AM110" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -13826,7 +13826,7 @@
         <v>0</v>
       </c>
       <c r="AM112" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -13945,7 +13945,7 @@
         <v>0</v>
       </c>
       <c r="AM113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114">
@@ -14302,7 +14302,7 @@
         <v>0</v>
       </c>
       <c r="AM116" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117">
@@ -14421,7 +14421,7 @@
         <v>0</v>
       </c>
       <c r="AM117" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118">
@@ -14778,7 +14778,7 @@
         <v>0</v>
       </c>
       <c r="AM120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121">
@@ -14897,7 +14897,7 @@
         <v>0</v>
       </c>
       <c r="AM121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122">
@@ -15135,6 +15135,363 @@
         <v>0</v>
       </c>
       <c r="AM123" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" t="n">
+        <v>1</v>
+      </c>
+      <c r="C124" t="n">
+        <v>4</v>
+      </c>
+      <c r="D124" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E124" t="n">
+        <v>3</v>
+      </c>
+      <c r="F124" t="n">
+        <v>3</v>
+      </c>
+      <c r="G124" t="n">
+        <v>6</v>
+      </c>
+      <c r="H124" t="n">
+        <v>1</v>
+      </c>
+      <c r="I124" t="n">
+        <v>8</v>
+      </c>
+      <c r="J124" t="n">
+        <v>4</v>
+      </c>
+      <c r="K124" t="n">
+        <v>1</v>
+      </c>
+      <c r="L124" t="n">
+        <v>1</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" t="n">
+        <v>1</v>
+      </c>
+      <c r="C125" t="n">
+        <v>5</v>
+      </c>
+      <c r="D125" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E125" t="n">
+        <v>2</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" t="n">
+        <v>3</v>
+      </c>
+      <c r="H125" t="n">
+        <v>1</v>
+      </c>
+      <c r="I125" t="n">
+        <v>2</v>
+      </c>
+      <c r="J125" t="n">
+        <v>1</v>
+      </c>
+      <c r="K125" t="n">
+        <v>1</v>
+      </c>
+      <c r="L125" t="n">
+        <v>1</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" t="n">
+        <v>1</v>
+      </c>
+      <c r="C126" t="n">
+        <v>4</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" t="n">
+        <v>4</v>
+      </c>
+      <c r="G126" t="n">
+        <v>6</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="n">
+        <v>1</v>
+      </c>
+      <c r="J126" t="n">
+        <v>4</v>
+      </c>
+      <c r="K126" t="n">
+        <v>1</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" t="n">
+        <v>1</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="n">
+        <v>1</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0</v>
+      </c>
+      <c r="U126" t="n">
+        <v>1</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0</v>
+      </c>
+      <c r="W126" t="n">
+        <v>1</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM126" t="n">
         <v>4</v>
       </c>
     </row>
